--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4370,6 +4370,220 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125900819</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91180</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fiholmsvik, Fiholmsvik, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>576153</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6594480</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tove Lundmark</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tove Lundmark</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125901001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91180</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fiholmsvik, Fiholmsvik, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>576132</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6594392</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tove Lundmark</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tove Lundmark</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91180</v>
+        <v>91187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91180</v>
+        <v>91187</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91187</v>
+        <v>91188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91187</v>
+        <v>91188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91188</v>
+        <v>91192</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91188</v>
+        <v>91192</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91192</v>
+        <v>91194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91192</v>
+        <v>91194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91194</v>
+        <v>91196</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91194</v>
+        <v>91196</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91196</v>
+        <v>91198</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91196</v>
+        <v>91198</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91198</v>
+        <v>91202</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91198</v>
+        <v>91202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -4375,7 +4375,7 @@
         <v>125900819</v>
       </c>
       <c r="B34" t="n">
-        <v>91202</v>
+        <v>91205</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>125901001</v>
       </c>
       <c r="B35" t="n">
-        <v>91202</v>
+        <v>91205</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113397</v>
+        <v>69084418</v>
       </c>
       <c r="B2" t="n">
-        <v>93234</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575959.1153123479</v>
+        <v>575875</v>
       </c>
       <c r="R2" t="n">
-        <v>6594246.385841215</v>
+        <v>6594480</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,78 +756,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandsko</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>475895</v>
+        <v>69084427</v>
       </c>
       <c r="B3" t="n">
-        <v>93374</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576011.5489933342</v>
+        <v>576100</v>
       </c>
       <c r="R3" t="n">
-        <v>6594296.734773178</v>
+        <v>6594451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,76 +856,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>474962</v>
+        <v>113397</v>
       </c>
       <c r="B4" t="n">
-        <v>81974</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1633</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rökpipsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Urnula craterium</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiholmsvik, Trossön, Vstm</t>
+          <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575934.686502947</v>
+        <v>575959</v>
       </c>
       <c r="R4" t="n">
-        <v>6594448.135871519</v>
+        <v>6594246</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,27 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2008-03-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2008-03-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Blandskog och ädellövskog med hassel i norr- och västsluttningar intill Mälaren. Imponerande hasselbestånd finns spridda utmed sluttningarna några enstaka med en stamdiameter upp till 25 centimeter!</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,57 +965,58 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Blandsko</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69084447</v>
+        <v>69084412</v>
       </c>
       <c r="B5" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3884</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575839.7767699282</v>
+        <v>575909</v>
       </c>
       <c r="R5" t="n">
-        <v>6594409.129875632</v>
+        <v>6594297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,19 +1061,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,37 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69084443</v>
+        <v>69084420</v>
       </c>
       <c r="B6" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3884</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1201,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575843.0009853233</v>
+        <v>575874</v>
       </c>
       <c r="R6" t="n">
-        <v>6594425.963313497</v>
+        <v>6594487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,19 +1161,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,37 +1191,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69084439</v>
+        <v>69084421</v>
       </c>
       <c r="B7" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92729</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>517</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Skinntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Dentipellis fragilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Pers.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1316,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575842.7555388999</v>
+        <v>575902</v>
       </c>
       <c r="R7" t="n">
-        <v>6594438.153613204</v>
+        <v>6594493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,19 +1261,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,37 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69084445</v>
+        <v>69084426</v>
       </c>
       <c r="B8" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>1143</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575858.1528481947</v>
+        <v>576069</v>
       </c>
       <c r="R8" t="n">
-        <v>6594431.857911291</v>
+        <v>6594492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,19 +1361,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,37 +1391,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69084441</v>
+        <v>69084433</v>
       </c>
       <c r="B9" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>1177</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Brödmärgsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Perenniporia medulla-panis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Jacq.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575837.8515003199</v>
+        <v>576068</v>
       </c>
       <c r="R9" t="n">
-        <v>6594428.908448406</v>
+        <v>6594502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,19 +1461,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,37 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69084444</v>
+        <v>69084434</v>
       </c>
       <c r="B10" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3884</v>
+        <v>1177</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Brödmärgsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Perenniporia medulla-panis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Jacq.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1661,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575860.9602144618</v>
+        <v>576214</v>
       </c>
       <c r="R10" t="n">
-        <v>6594444.109674064</v>
+        <v>6594482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,19 +1561,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,37 +1591,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>69084449</v>
+        <v>69084410</v>
       </c>
       <c r="B11" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3884</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1776,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575903.7968355466</v>
+        <v>575943</v>
       </c>
       <c r="R11" t="n">
-        <v>6594313.871852316</v>
+        <v>6594268</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,19 +1661,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,37 +1691,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>69084446</v>
+        <v>69084423</v>
       </c>
       <c r="B12" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3884</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575947.925799435</v>
+        <v>575955</v>
       </c>
       <c r="R12" t="n">
-        <v>6594447.894652923</v>
+        <v>6594504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,19 +1761,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,15 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69084434</v>
+        <v>69084411</v>
       </c>
       <c r="B13" t="n">
-        <v>89966</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1177</v>
+        <v>2014</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brödmärgsticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perenniporia medulla-panis</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Jacq.) Donk</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2006,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576213.9562600461</v>
+        <v>575913</v>
       </c>
       <c r="R13" t="n">
-        <v>6594482.231469396</v>
+        <v>6594275</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,19 +1861,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,15 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69084440</v>
+        <v>475895</v>
       </c>
       <c r="B14" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,36 +1902,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3884</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575832.1727605711</v>
+        <v>576012</v>
       </c>
       <c r="R14" t="n">
-        <v>6594432.859202757</v>
+        <v>6594297</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,22 +1956,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,71 +1970,68 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>69084433</v>
+        <v>727349</v>
       </c>
       <c r="B15" t="n">
-        <v>89966</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1177</v>
+        <v>2671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brödmärgsticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perenniporia medulla-panis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Jacq.) Donk</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576067.9762700468</v>
+        <v>575813</v>
       </c>
       <c r="R15" t="n">
-        <v>6594502.146410991</v>
+        <v>6594245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2266,22 +2058,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,34 +2072,38 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>69084450</v>
+        <v>1025748</v>
       </c>
       <c r="B16" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,36 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Trossön, Vstm</t>
+          <t>GAMMAL LIND O EK N. TROSSÖN (10G9g45), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575866.7831521139</v>
+        <v>575863</v>
       </c>
       <c r="R16" t="n">
-        <v>6594230.804824032</v>
+        <v>6594385</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,22 +2165,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-09-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>100696451 / ANTI CUR / Allmän-riklig (3)  / AJO / OBJ.AREA:0 ha</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,34 +2184,42 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Mossblock</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>69084414</v>
+        <v>72071186</v>
       </c>
       <c r="B17" t="n">
-        <v>86314</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,35 +2227,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4392</v>
+        <v>2779</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575852.8677846809</v>
+        <v>576008</v>
       </c>
       <c r="R17" t="n">
-        <v>6594466.812645692</v>
+        <v>6594502</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2492,22 +2281,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,56 +2295,50 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>69084427</v>
+        <v>69084439</v>
       </c>
       <c r="B18" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>3884</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576100.0599128086</v>
+        <v>575843</v>
       </c>
       <c r="R18" t="n">
-        <v>6594450.965140925</v>
+        <v>6594438</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,19 +2383,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,37 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>69084421</v>
+        <v>69084440</v>
       </c>
       <c r="B19" t="n">
-        <v>90171</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>517</v>
+        <v>3884</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinntagging</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dentipellis fragilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) Donk</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2692,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575902.2191383562</v>
+        <v>575832</v>
       </c>
       <c r="R19" t="n">
-        <v>6594493.213227613</v>
+        <v>6594433</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2725,19 +2483,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,37 +2513,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>69084420</v>
+        <v>69084441</v>
       </c>
       <c r="B20" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>366</v>
+        <v>3884</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2807,10 +2550,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575873.838671695</v>
+        <v>575838</v>
       </c>
       <c r="R20" t="n">
-        <v>6594487.052043992</v>
+        <v>6594429</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,19 +2583,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>69084428</v>
+        <v>69084443</v>
       </c>
       <c r="B21" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,21 +2624,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4660</v>
+        <v>3884</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2922,10 +2650,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576106.9985206902</v>
+        <v>575843</v>
       </c>
       <c r="R21" t="n">
-        <v>6594460.251732309</v>
+        <v>6594426</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2955,19 +2683,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,15 +2713,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>69084424</v>
+        <v>69084444</v>
       </c>
       <c r="B22" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,21 +2724,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4660</v>
+        <v>3884</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3037,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575999.8612226854</v>
+        <v>575861</v>
       </c>
       <c r="R22" t="n">
-        <v>6594548.026956753</v>
+        <v>6594444</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,19 +2783,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,37 +2813,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>69084418</v>
+        <v>69084445</v>
       </c>
       <c r="B23" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>3884</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3152,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575874.9995190059</v>
+        <v>575858</v>
       </c>
       <c r="R23" t="n">
-        <v>6594479.961630243</v>
+        <v>6594432</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3185,19 +2883,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,37 +2913,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>69084412</v>
+        <v>69084446</v>
       </c>
       <c r="B24" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>366</v>
+        <v>3884</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3267,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575909.2228942488</v>
+        <v>575948</v>
       </c>
       <c r="R24" t="n">
-        <v>6594297.212159045</v>
+        <v>6594448</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3300,19 +2983,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,15 +3013,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>69084407</v>
+        <v>69084447</v>
       </c>
       <c r="B25" t="n">
-        <v>86132</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,21 +3024,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4374</v>
+        <v>3884</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3382,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576087.8737695807</v>
+        <v>575840</v>
       </c>
       <c r="R25" t="n">
-        <v>6594172.251217503</v>
+        <v>6594409</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3415,19 +3083,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3455,37 +3113,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>69084411</v>
+        <v>69084449</v>
       </c>
       <c r="B26" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2014</v>
+        <v>3884</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3497,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575913.2351007021</v>
+        <v>575904</v>
       </c>
       <c r="R26" t="n">
-        <v>6594274.934186877</v>
+        <v>6594314</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3530,19 +3183,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3570,37 +3213,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>69084416</v>
+        <v>69084450</v>
       </c>
       <c r="B27" t="n">
-        <v>89383</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4661</v>
+        <v>3884</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Almsprängticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Inonotus ulmicola</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Corfixen</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3612,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575852.8449046218</v>
+        <v>575867</v>
       </c>
       <c r="R27" t="n">
-        <v>6594392.116269197</v>
+        <v>6594231</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,19 +3283,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3685,37 +3313,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>69084423</v>
+        <v>69084453</v>
       </c>
       <c r="B28" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>3884</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3727,10 +3350,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575954.9401193643</v>
+        <v>576128</v>
       </c>
       <c r="R28" t="n">
-        <v>6594503.930373473</v>
+        <v>6594550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,19 +3383,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3800,55 +3413,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>69084417</v>
+        <v>73855528</v>
       </c>
       <c r="B29" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575833.0190163405</v>
+        <v>576247</v>
       </c>
       <c r="R29" t="n">
-        <v>6594416.107750692</v>
+        <v>6594468</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3872,22 +3492,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-11-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,6 +3510,19 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>ekskog</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>1 substratenheter # stående död hasselgren</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -3908,62 +3531,55 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>69084426</v>
+        <v>72071187</v>
       </c>
       <c r="B30" t="n">
-        <v>89953</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81655</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1143</v>
+        <v>3929</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576069.1990254148</v>
+        <v>576149</v>
       </c>
       <c r="R30" t="n">
-        <v>6594492.008548939</v>
+        <v>6594547</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3987,22 +3603,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4011,56 +3617,50 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>69084410</v>
+        <v>69084407</v>
       </c>
       <c r="B31" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>4374</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4072,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575942.9010292557</v>
+        <v>576088</v>
       </c>
       <c r="R31" t="n">
-        <v>6594267.909776282</v>
+        <v>6594172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4105,19 +3705,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4145,15 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>69084415</v>
+        <v>69084414</v>
       </c>
       <c r="B32" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,23 +3746,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5420</v>
+        <v>4392</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -4187,10 +3768,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575831.9264571689</v>
+        <v>575853</v>
       </c>
       <c r="R32" t="n">
-        <v>6594242.807021901</v>
+        <v>6594467</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4220,19 +3801,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,15 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>72071186</v>
+        <v>69084424</v>
       </c>
       <c r="B33" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4276,37 +3842,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2779</v>
+        <v>4660</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576007.9170508611</v>
+        <v>576000</v>
       </c>
       <c r="R33" t="n">
-        <v>6594501.950258046</v>
+        <v>6594548</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4330,22 +3898,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4354,66 +3912,69 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125900819</v>
+        <v>69084428</v>
       </c>
       <c r="B34" t="n">
-        <v>91205</v>
+        <v>91893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5445</v>
+        <v>4660</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiholmsvik, Fiholmsvik, Vstm</t>
+          <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576153</v>
+        <v>576107</v>
       </c>
       <c r="R34" t="n">
-        <v>6594480</v>
+        <v>6594460</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4437,22 +3998,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>20:59</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>20:59</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4461,66 +4012,69 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125901001</v>
+        <v>69084416</v>
       </c>
       <c r="B35" t="n">
-        <v>91205</v>
+        <v>91900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5445</v>
+        <v>4661</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Almsprängticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Inonotus ulmicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Corfixen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fiholmsvik, Fiholmsvik, Vstm</t>
+          <t>Trossön, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576132</v>
+        <v>575853</v>
       </c>
       <c r="R35" t="n">
         <v>6594392</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4544,22 +4098,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>20:59</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>20:59</t>
+          <t>2006-12-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,21 +4112,747 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>69084409</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Trossön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>575836</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6594215</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>69084425</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Trossön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>576123</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6594547</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>69084415</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92348</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Trossön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>575832</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6594243</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>69084417</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Trossön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>575833</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6594416</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125900819</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fiholmsvik, Fiholmsvik, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>576153</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6594480</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Tove Lundmark</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Tove Lundmark</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125901001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fiholmsvik, Fiholmsvik, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>576132</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6594392</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tove Lundmark</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tove Lundmark</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5250415</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>GAMMAL LIND O EK N. TROSSÖN (10G9g45), Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>575863</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6594385</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rytterne</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1997-09-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1997-09-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>100696451 / ACTA SPI / Allmän-riklig (3)  / AJO / OBJ.AREA:0 ha</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18213-2022 artfynd.xlsx
+++ b/artfynd/A 18213-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084418</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084427</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113397</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084412</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084420</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084421</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084426</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084434</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084411</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/475895</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1897,6 +1957,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/727349</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1025748</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,6 +2183,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084439</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2213,6 +2288,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084440</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2313,6 +2393,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084441</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084443</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2513,6 +2603,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084444</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084445</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,6 +2813,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084446</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084447</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2913,6 +3023,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084449</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3013,6 +3128,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084450</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3138,6 +3258,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73855528</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3238,6 +3363,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084407</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3334,6 +3464,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084414</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3434,6 +3569,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084428</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3534,6 +3674,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084416</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3634,6 +3779,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084409</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3734,6 +3884,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084415</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3834,6 +3989,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084417</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3941,6 +4101,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125900819</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4048,6 +4213,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125901001</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4159,6 +4329,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5250415</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4259,6 +4434,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084433</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4359,6 +4539,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084423</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4456,6 +4641,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72071186</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4556,6 +4746,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084453</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4653,6 +4848,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72071187</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4753,6 +4953,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084424</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4853,8 +5058,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69084425</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>